--- a/Results/data_reduction_results/diagnostics/pam_parametrizer_diagnostics_datareduc_40_5.xlsx
+++ b/Results/data_reduction_results/diagnostics/pam_parametrizer_diagnostics_datareduc_40_5.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Best_Individuals" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Computational_Time" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Final_Errors" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="translational_sector" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sector_parameters" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="reaction_weights" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P09053</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -480,14 +480,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CE_VPAMTr_P09053</t>
+          <t>CE_ASPTA_P00509</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.375782643037973</v>
+        <v>3.547748006805836</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="3">
@@ -496,7 +496,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P09053</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -506,14 +506,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CE_VPAMTr_P09053</t>
+          <t>CE_ASPTA_P00509</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5.623355192633744</v>
+        <v>4.799895433454638</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="4">
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P0A6P9</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,14 +532,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CE_ENO_P0A6P9</t>
+          <t>CE_CYSTA_P00509</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7.746295151927729</v>
+        <v>1.997716914102064</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="5">
@@ -548,7 +548,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P0A6P9</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -558,14 +558,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CE_ENO_P0A6P9</t>
+          <t>CE_CYSTA_P00509</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30.78253258294341</v>
+        <v>16.74043972652385</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="6">
@@ -574,7 +574,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P0A825</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -584,14 +584,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CE_GHMT2r_P0A825</t>
+          <t>CE_PHETA1_P00509</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.431527280371899</v>
+        <v>4.138055626171921</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="7">
@@ -600,7 +600,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P0A825</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -610,14 +610,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CE_GHMT2r_P0A825</t>
+          <t>CE_PHETA1_P00509</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.2811879633755921</v>
+        <v>1.571244053046029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="8">
@@ -626,7 +626,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P0A9B2</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CE_E4PD_P0A9B2</t>
+          <t>CE_TYRTA_P00509</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>63.70684186416143</v>
+        <v>7.160095218906336</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="9">
@@ -652,24 +652,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P0A9Q5_P0ABD8_P24182_P0ABD5</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CE_ACCOAC_P0A9Q5_P0ABD8_P24182_P0ABD5</t>
+          <t>CE_TYRTA_P00509</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.346280704639673</v>
+        <v>0.7614134012399001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="10">
@@ -678,24 +678,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P0A9Q5_P0ABD8_P24182_P0ABD5</t>
+          <t>P06149</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CE_ACCOAC_P0A9Q5_P0ABD8_P24182_P0ABD5</t>
+          <t>CE_LDH_D2_P06149</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.67581081700095</v>
+        <v>71.58169933775609</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="11">
@@ -704,24 +704,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P0AB80</t>
+          <t>P08200</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PHETA1</t>
+          <t>CE_ICDHyr_P08200</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29.00452567155748</v>
+        <v>13.93574246913021</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="12">
@@ -730,7 +730,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P0ABC0_P0A6E6_P0ABA6_P0ABA4_P0ABB0_P0ABB4_P0AB98_P0ABA0_P68699</t>
+          <t>P08200</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -740,14 +740,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CE_ATPS4rpp_P0ABC0_P0A6E6_P0ABA6_P0ABA4_P0ABB0_P0ABB4_P0AB98_P0ABA0_P68699</t>
+          <t>CE_ICDHyr_P08200</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67.06429507479085</v>
+        <v>4.15524783873585</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="13">
@@ -756,24 +756,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>P08839_P0AA04_P37349_P76014_P76015</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CE_CYTBO3_4pp_P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>CE_DHAPT_P08839_P0AA04_P37349_P76014_P76015</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10.85913250567604</v>
+        <v>259.926539172408</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="14">
@@ -782,7 +782,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P08839_P0AA04_P37349_P76014_P76015</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -792,14 +792,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_DHAPT_P08839_P0AA04_P37349_P76014_P76015</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.04542126877828845</v>
+        <v>59.4178151609736</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="15">
@@ -808,24 +808,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P68699</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P68699</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.09406993126910829</v>
+        <v>48.04136379455754</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="16">
@@ -834,24 +834,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P77399</t>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P68699</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CE_ECOAH3_P77399</t>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P68699</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.516698238704267</v>
+        <v>204.5891518038592</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="17">
@@ -860,7 +860,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P77399</t>
+          <t>P0A6P9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -870,19 +870,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CE_ECOAH3_P77399</t>
+          <t>CE_ENO_P0A6P9</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100.2129633663211</v>
+        <v>30.44366913653072</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03660384684353007</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -900,71 +900,71 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.304881713397297</v>
+        <v>35.04925108959584</v>
       </c>
       <c r="F18" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P0A6P9</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CE_ENO_P0A6P9</t>
+          <t>CE_ILETA_P0AB80</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>95.03666563865227</v>
+        <v>0.2267420052297043</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P0A955</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CE_OAADC_P0A955</t>
+          <t>CE_ILETA_P0AB80</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>123.8908408017818</v>
+        <v>0.6803546934102452</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P0A9B2</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -974,71 +974,71 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CE_E4PD_P0A9B2</t>
+          <t>CE_LEUTAi_P0AB80</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>34.71466538084848</v>
+        <v>1.107070257313132</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P0A9Q5_P0ABD8_P24182_P0ABD5</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CE_ACCOAC_P0A9Q5_P0ABD8_P24182_P0ABD5</t>
+          <t>CE_LEUTAi_P0AB80</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2259576862384855</v>
+        <v>0.9254837346895336</v>
       </c>
       <c r="F22" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>P0A9Q5_P0ABD8_P24182_P0ABD5</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CE_ACCOAC_P0A9Q5_P0ABD8_P24182_P0ABD5</t>
+          <t>CE_VALTA_P0AB80</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>34.04043383006451</v>
+        <v>3.903371339558046</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1047,28 +1047,28 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CE_PHETA1_P0AB80</t>
+          <t>CE_VALTA_P0AB80</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>40.49540181974975</v>
+        <v>0.09045745957745041</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P0AB89</t>
+          <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1078,170 +1078,170 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CE_ADSL2r_P0AB89</t>
+          <t>CE_CYTBO3_4pp_P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.867918309642187</v>
+        <v>60.24170728140404</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>P0AB89</t>
+          <t>P15640</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CE_ADSL2r_P0AB89</t>
+          <t>CE_PRAGSr_P15640</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>31.96703928518247</v>
+        <v>6.375162847447562</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>P15640</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CE_CYTBO3_4pp_P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>CE_PRAGSr_P15640</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10.75791516077292</v>
+        <v>26.57494310776917</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P25516</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_ACONTa_P25516</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.04542126877828844</v>
+        <v>195.7398277820841</v>
       </c>
       <c r="F28" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P25516</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_ACONTa_P25516</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.1015333600530081</v>
+        <v>15.78059376877559</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P52697</t>
+          <t>P25516</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CE_PGL_P52697</t>
+          <t>CE_ACONTb_P25516</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9.8454</v>
+        <v>11.91322248613984</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P52697</t>
+          <t>P25516</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CE_PGL_P52697</t>
+          <t>CE_ACONTb_P25516</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>28.77042246973551</v>
+        <v>140.0358922751531</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.5411445543572136</v>
       </c>
     </row>
     <row r="32">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P77399</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1260,14 +1260,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ECOAH4</t>
+          <t>CE_TYRTA_P00509</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.5615975471449781</v>
+        <v>5.469382674635592</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="33">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>P77399</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1286,205 +1286,205 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ECOAH4</t>
+          <t>CE_TYRTA_P00509</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>65.02742131506001</v>
+        <v>0.3579547432174691</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04406808951006189</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P00562</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HSDy</t>
+          <t>CE_PHETA1_P00509</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>9.860964595912952</v>
+        <v>1.14917063473918</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>P00562</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HSDy</t>
+          <t>CE_PHETA1_P00509</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>7.266327558899718</v>
+        <v>1.395573055287188</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>P0A6P9</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CE_ENO_P0A6P9</t>
+          <t>CE_CYSTA_P00509</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>36.47523605561204</v>
+        <v>9.403013187984785</v>
       </c>
       <c r="F36" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>P0A6P9</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CE_ENO_P0A6P9</t>
+          <t>CE_CYSTA_P00509</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1041.80974099788</v>
+        <v>2.370884109058263</v>
       </c>
       <c r="F37" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>P0A825</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CE_GHMT2r_P0A825</t>
+          <t>CE_ASPTA_P00509</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>14.92476188971361</v>
+        <v>3.307472932902686</v>
       </c>
       <c r="F38" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>P0A825</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CE_GHMT2r_P0A825</t>
+          <t>CE_ASPTA_P00509</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.1946945992287459</v>
+        <v>2.250977145965771</v>
       </c>
       <c r="F39" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>P0A9B2</t>
+          <t>P08200</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NADHHS</t>
+          <t>CE_ICDHyr_P08200</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>110.8251127745914</v>
+        <v>14.8912279006232</v>
       </c>
       <c r="F40" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>P0AB80</t>
+          <t>P08200</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1494,75 +1494,75 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CE_PHETA1_P0AB80</t>
+          <t>CE_ICDHyr_P08200</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>21.25629975383765</v>
+        <v>5.657535411706375</v>
       </c>
       <c r="F41" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>P0AB89</t>
+          <t>P08839_P0AA04_P37349_P76014_P76015</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CE_ADSL2r_P0AB89</t>
+          <t>CE_DHAPT_P08839_P0AA04_P37349_P76014_P76015</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>39.39829870783996</v>
+        <v>518.4601464219127</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>P0AB89</t>
+          <t>P08839_P0AA04_P37349_P76014_P76015</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CE_ADSL2r_P0AB89</t>
+          <t>CE_DHAPT_P08839_P0AA04_P37349_P76014_P76015</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>115.7359824265414</v>
+        <v>27.5061331581584</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1572,49 +1572,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CE_CYTBO3_4pp_P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9.593221165523939</v>
+        <v>139.1796871817847</v>
       </c>
       <c r="F44" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.03292281035618342</v>
+        <v>112.7589041685043</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P0A6P9</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1624,23 +1624,23 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_ENO_P0A6P9</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0870251212529238</v>
+        <v>37.03593149473137</v>
       </c>
       <c r="F46" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>P76015_P37349_P08839_P0AA04_P76014</t>
+          <t>P0A6P9</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1650,49 +1650,49 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CE_DHAPT_P76015_P37349_P08839_P0AA04_P76014</t>
+          <t>CE_ENO_P0A6P9</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>70.37892563270967</v>
+        <v>68.44141667544557</v>
       </c>
       <c r="F47" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>P76015_P37349_P08839_P0AA04_P76014</t>
+          <t>P0A754</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CE_DHAPT_P76015_P37349_P08839_P0AA04_P76014</t>
+          <t>CE_NADH10_P0A754</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.201839020798436</v>
+        <v>144.8943708290624</v>
       </c>
       <c r="F48" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>P77399</t>
+          <t>P0A754</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1702,23 +1702,23 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CE_ECOAH8_P77399</t>
+          <t>CE_NADH5_P0A754</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>32.99999999999999</v>
+        <v>49.2118016074411</v>
       </c>
       <c r="F49" t="n">
-        <v>0.05500650591619388</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>P0A6P9</t>
+          <t>P0A754</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1728,75 +1728,75 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CE_ENO_P0A6P9</t>
+          <t>CE_NADH9_P0A754</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>98.03460444473863</v>
+        <v>101.1702191434372</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>P0A6P9</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CE_ENO_P0A6P9</t>
+          <t>CE_VALTA_P0AB80</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>924.4823933069438</v>
+        <v>3.833396045613569</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>P0A9B2</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NADPHHR</t>
+          <t>CE_LEUTAi_P0AB80</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>34.68037663835938</v>
+        <v>0.4656587723529828</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>P0A9G6</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1806,23 +1806,23 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CE_ICL_P0A9G6</t>
+          <t>CE_LEUTAi_P0AB80</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.1252</v>
+        <v>1.710740001041308</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>P0A9G6</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1832,19 +1832,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CE_ICL_P0A9G6</t>
+          <t>CE_ILETA_P0AB80</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.1252</v>
+        <v>0.5251402547029098</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1858,19 +1858,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CE_LEUTAi_P0AB80</t>
+          <t>CE_ILETA_P0AB80</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>21.07265680857345</v>
+        <v>0.078093011670653</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1884,23 +1884,23 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CE_LEUTAi_P0AB80</t>
+          <t>CE_VALTA_P0AB80</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.3538027113073398</v>
+        <v>0.03704999201354676</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1910,23 +1910,23 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CE_CYTBO3_4pp_P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>CE_CYTBO3_4pp_P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>9.593221165523937</v>
+        <v>43.20797449460665</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>P0AFG6_P0A9P0_P0AFG3</t>
+          <t>P33570</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1936,23 +1936,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CE_AKGDH_P0AFG6_P0A9P0_P0AFG3</t>
+          <t>CE_TKT1_P33570</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2165.715711070929</v>
+        <v>61.56974606034843</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>P0AFG6_P0A9P0_P0AFG3</t>
+          <t>P33570</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1962,101 +1962,101 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CE_AKGDH_P0AFG6_P0A9P0_P0AFG3</t>
+          <t>CE_TKT1_P33570</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.116200000000001</v>
+        <v>49.57346466366105</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P33570</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_TKT2_P33570</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.03292281035618343</v>
+        <v>7.082699888803152</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P33570</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_TKT2_P33570</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.0870251212529238</v>
+        <v>20.87054740493226</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>P25516</t>
+          <t>P36683</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CE_ACONTb_P25516</t>
+          <t>CE_MICITDr_P36683</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>15.33558682322717</v>
+        <v>27.79699433507799</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>P25516</t>
+          <t>P36683</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2066,19 +2066,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CE_ACONTb_P25516</t>
+          <t>CE_ACONTb_P36683</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>13.3722</v>
+        <v>22.99386883305798</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2096,15 +2096,15 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>13.3722</v>
+        <v>251.593333966732</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2113,54 +2113,54 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CE_ACONTb_P36683</t>
+          <t>CE_ACONTa_P36683</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>7.119513040982959</v>
+        <v>274.1995997866583</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>P77399</t>
+          <t>P36683</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ECOAH7</t>
+          <t>CE_MICITDr_P36683</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>46.29011938766161</v>
+        <v>3.447362298944747</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>P77399</t>
+          <t>P36683</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2170,101 +2170,101 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ECOAH7</t>
+          <t>CE_ACONTa_P36683</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6.648824485827473</v>
+        <v>25.37730830565162</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0405020509034568</v>
+        <v>0.867786430567393</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>P00562</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CE_ASPK_P00562</t>
+          <t>CE_TYRTA_P00509</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>19.72619252226204</v>
+        <v>0.37492677706679</v>
       </c>
       <c r="F68" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>P00562</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CE_ASPK_P00562</t>
+          <t>CE_ASPTA_P00509</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>15.99903828406964</v>
+        <v>1.49105634599115</v>
       </c>
       <c r="F69" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>P0A9B2</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NADHHR</t>
+          <t>CE_ASPTA_P00509</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>44.13779443842889</v>
+        <v>2.396394522288107</v>
       </c>
       <c r="F70" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>P0A9G6</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2274,23 +2274,23 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CE_ICL_P0A9G6</t>
+          <t>CE_CYSTA_P00509</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>31.91066670186766</v>
+        <v>1.865179079847964</v>
       </c>
       <c r="F71" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>P0A9G6</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2300,23 +2300,23 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CE_ICL_P0A9G6</t>
+          <t>CE_CYSTA_P00509</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2.908348105718486</v>
+        <v>5.765253186441433</v>
       </c>
       <c r="F72" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>P0AB80</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2326,23 +2326,23 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CE_LEUTAi_P0AB80</t>
+          <t>CE_PHETA1_P00509</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>12.54589753330734</v>
+        <v>1.10918159437294</v>
       </c>
       <c r="F73" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>P0AB80</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2352,23 +2352,23 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CE_LEUTAi_P0AB80</t>
+          <t>CE_PHETA1_P00509</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2.006544567009185</v>
+        <v>1.05889419402831</v>
       </c>
       <c r="F74" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2378,23 +2378,23 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CE_CYTBO3_4pp_P0ABJ1_P0ABI8_P0ABJ6_P0ABJ3</t>
+          <t>CE_TYRTA_P00509</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5.804496807795676</v>
+        <v>18.05137787761256</v>
       </c>
       <c r="F75" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>P0AFG6_P0A9P0_P0AFG3</t>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2404,23 +2404,23 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CE_AKGDH_P0AFG6_P0A9P0_P0AFG3</t>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2.914354278331966</v>
+        <v>222.7518179923154</v>
       </c>
       <c r="F76" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>P0AFG6_P0A9P0_P0AFG3</t>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2430,23 +2430,23 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CE_AKGDH_P0AFG6_P0A9P0_P0AFG3</t>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4105.853955031538</v>
+        <v>111.7286332142859</v>
       </c>
       <c r="F77" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P0A6P9</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2456,23 +2456,23 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_ENO_P0A6P9</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.03292281035618343</v>
+        <v>37.04474205158407</v>
       </c>
       <c r="F78" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>P15640</t>
+          <t>P0A6P9</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2482,170 +2482,3706 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CE_PRAGSr_P15640</t>
+          <t>CE_ENO_P0A6P9</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.02684496729053571</v>
+        <v>26.04662718596309</v>
       </c>
       <c r="F79" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>P25516</t>
+          <t>P0AB71</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CE_ACONTb_P25516</t>
+          <t>CE_FBA3_P0AB71</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>7.897009125590925</v>
+        <v>14.3390628041421</v>
       </c>
       <c r="F80" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>P25516</t>
+          <t>P0AB71</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CE_ACONTb_P25516</t>
+          <t>CE_FBA3_P0AB71</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>13.23827152666803</v>
+        <v>55.30599799287312</v>
       </c>
       <c r="F81" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>P36683</t>
+          <t>P0AB71</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CE_MICITDr_P36683</t>
+          <t>CE_FBA_P0AB71</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>893.9016339229161</v>
+        <v>3.476562490676268</v>
       </c>
       <c r="F82" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>P36683</t>
+          <t>P0AB71</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CE_MICITDr_P36683</t>
+          <t>CE_FBA_P0AB71</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>76.975989491419</v>
+        <v>18.96620645872614</v>
       </c>
       <c r="F83" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>P77399</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ECOAH3</t>
+          <t>CE_ILETA_P0AB80</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>82800.78801371386</v>
+        <v>0.4043127702897715</v>
       </c>
       <c r="F84" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>P77399</t>
+          <t>P0AB80</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ECOAH3</t>
+          <t>CE_LEUTAi_P0AB80</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>47.99459223660669</v>
+        <v>2.535217084469001</v>
       </c>
       <c r="F85" t="n">
-        <v>0.06160476769056775</v>
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CE_LEUTAi_P0AB80</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.2926701958605692</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>3</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CE_VALTA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6.562519217661148</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CE_VALTA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.03533938042083816</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>3</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CE_ILETA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.03447186816765295</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CE_CYTBO3_4pp_P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>33.79160498450679</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CE_NADH16pp_P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>151.3416112705322</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CE_NADH17pp_P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>68.96763567026207</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CE_NADH18pp_P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>55.59327260373147</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>P0AGE6</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CE_NADH10_P0AGE6</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100.9276704114434</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>P0AGE6</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CE_NADH5_P0AGE6</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>125.487759641279</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>3</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>P0AGE6</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CE_NADH9_P0AGE6</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>32.61478746473292</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>P33570</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CE_TKT1_P33570</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>95.93011631521209</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>P33570</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CE_TKT1_P33570</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>126.8560977863716</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>3</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>P33570</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CE_TKT2_P33570</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>20.20817342021875</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>P33570</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CE_TKT2_P33570</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>3.976768775946323</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>3</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>P36683</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CE_ACONTa_P36683</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>12.98729670580758</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>P36683</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CE_ACONTa_P36683</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>406.8674198901577</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>3</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>P36683</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CE_ACONTb_P36683</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>125.2700503526015</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>3</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>P36683</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CE_ACONTb_P36683</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>28.61062317162533</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>3</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>P36683</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CE_MICITDr_P36683</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1.157901460575443</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>3</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>P36683</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CE_MICITDr_P36683</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>27.79699433507799</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.8724642531793906</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CE_PHETA1_P00509</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1.10918159437294</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CE_TYRTA_P00509</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.37492677706679</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>CE_TYRTA_P00509</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>18.05137787761256</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>CE_PHETA1_P00509</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1.05889419402831</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>CE_CYSTA_P00509</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>5.765253186441433</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CE_ASPTA_P00509</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1.276677231308916</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CE_ASPTA_P00509</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>2.396394522288107</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CE_CYSTA_P00509</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1.865179079847964</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>P09053</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CE_VPAMTr_P09053</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>16.62760618855338</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>P09053</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CE_VPAMTr_P09053</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>4.801076597247647</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>150.7194555678109</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>37.77995834686536</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>P0A6P9</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CE_ENO_P0A6P9</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>37.04474205158407</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>P0A6P9</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CE_ENO_P0A6P9</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>26.04662718596309</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CE_GHMT2r_P0A825</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>5.311922064285238</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CE_GHMT2r_P0A825</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4719206904034935</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CE_THFAT_P0A825</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>121.1557621163821</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CE_ALATA_L2_P0A825</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>59.63604062572988</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CE_ALATA_D2_P0A825</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>107.431010699197</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>CE_THFAT_P0A825</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>81.94520130518899</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CE_THRA2_P0A825</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>62.65156853148129</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>CE_LEUTAi_P0AB80</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>2.535217084469001</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CE_VALTA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6.562519217661148</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CE_LEUTAi_P0AB80</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0.2926701958605692</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>4</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CE_ILETA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0.4043127702897716</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>CE_ILETA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0.03447186816765294</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CE_VALTA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0.03533938042083816</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CE_ADSL1r_P0AB89</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>2.957840952930592</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>CE_ADSL1r_P0AB89</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>131.6908687630315</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CE_ADSL2r_P0AB89</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>3.053529222792632</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CE_ADSL2r_P0AB89</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>49.45052612205559</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CE_CYTBO3_4pp_P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>45.51598150771412</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CE_NADH18pp_P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>35.55079965829727</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>CE_NADH17pp_P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>64.30306329642511</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CE_NADH16pp_P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>100.5006118460251</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>P52697</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CE_PGL_P52697</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>18.4709</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>P52697</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CE_PGL_P52697</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>22.97260000000001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.8726859612877762</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>5</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>P00350</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CE_GND_P00350</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>88.59970000000001</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>5</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>P00350</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CE_GND_P00350</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>74.1384</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>5</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CE_ASPTA_P00509</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>1.276677231308916</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>5</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CE_ASPTA_P00509</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>2.396394522288107</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>5</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CE_CYSTA_P00509</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>1.865179079847964</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>5</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>CE_CYSTA_P00509</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>5.765253186441433</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>5</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CE_PHETA1_P00509</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1.10918159437294</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>5</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>CE_PHETA1_P00509</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1.05889419402831</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>5</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CE_TYRTA_P00509</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>18.05137787761256</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>5</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CE_TYRTA_P00509</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0.37492677706679</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>5</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>P05793</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>CE_KARA1_P05793</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>5.691699999999999</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>5</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>P05793</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CE_KARA1_P05793</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>4.4149</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>5</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>P05793</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CE_KARA2_P05793</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>5</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>P05793</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CE_KARA2_P05793</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>5</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>P08200</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CE_ICDHyr_P08200</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>5.657535411706376</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>5</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>P08200</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>CE_ICDHyr_P08200</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>14.8912279006232</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>5</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>150.7194555678109</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>5</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>37.77995834686536</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>5</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>P0A6P9</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CE_ENO_P0A6P9</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>37.04474205158407</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>5</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>P0A6P9</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CE_ENO_P0A6P9</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>26.04662718596309</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>5</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>P0A754</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CE_NADH5_P0A754</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>49.2118016074411</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>5</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>P0A754</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CE_NADH9_P0A754</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>101.1702191434372</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>5</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>P0A754</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CE_NADH10_P0A754</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>144.8943708290624</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>5</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CE_THFAT_P0A825</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>121.1557621163821</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>5</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>CE_ALATA_L2_P0A825</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>59.63604062572988</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>5</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CE_ALATA_D2_P0A825</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>107.431010699197</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>5</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CE_THFAT_P0A825</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>81.94520130518899</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>5</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CE_THRA2_P0A825</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>62.65156853148129</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>5</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CE_GHMT2r_P0A825</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.4719206904034937</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>5</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CE_GHMT2r_P0A825</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>5.311922064285238</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>5</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>P0A8G6</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CE_NADH10_P0A8G6</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>5</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>P0A8G6</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>CE_NADH9_P0A8G6</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>5</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>P0A8G6</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CE_NADH5_P0A8G6</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>5</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CE_NADHHS_P0A9B2</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>5</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CE_NADPHHS_P0A9B2</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>5</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CE_NADPHHR_P0A9B2</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>5</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CE_NADHHR_P0A9B2</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>5</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CE_GAPD_P0A9B2</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>84.57050000000001</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>5</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CE_GAPD_P0A9B2</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>131.4733</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>5</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>P0AB71</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CE_FBA_P0AB71</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>3.476562490676268</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>5</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>P0AB71</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CE_FBA_P0AB71</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>18.96620645872614</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>5</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>P0AB71</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CE_FBA3_P0AB71</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>14.3390628041421</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>5</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>P0AB71</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CE_FBA3_P0AB71</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>55.30599799287312</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>5</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CE_VALTA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0.03533938042083816</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>5</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CE_VALTA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>6.562519217661148</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>5</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CE_LEUTAi_P0AB80</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0.2926701958605692</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>5</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CE_LEUTAi_P0AB80</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>2.535217084469001</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>5</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CE_ILETA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0.4043127702897716</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>5</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CE_ILETA_P0AB80</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0.03447186816765294</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>5</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CE_ADSL2r_P0AB89</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>49.45052612205559</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>5</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CE_ADSL2r_P0AB89</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>3.053529222792631</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>5</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CE_ADSL1r_P0AB89</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>131.6908687630315</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>5</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CE_ADSL1r_P0AB89</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>2.957840952930592</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>5</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CE_CYTBO3_4pp_P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>45.51598150771412</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>5</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CE_NADH18pp_P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>35.55079965829726</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>5</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CE_NADH16pp_P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>100.5006118460251</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>5</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CE_NADH17pp_P0AFC3_P0AFC7_P0AFD1_P0AFD4_P0AFD6_P0AFE0_P0AFE4_P0AFE8_P0AFF0_P31979_P33599_P33602_P33607</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>64.30306329642511</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>5</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>P0AGE6</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CE_NADH9_P0AGE6</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>32.61478746473292</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>5</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>P0AGE6</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CE_NADH5_P0AGE6</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>125.487759641279</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>5</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>P0AGE6</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CE_NADH10_P0AGE6</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>100.9276704114434</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>5</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CE_ACONTa_P25516</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>15.78059376877559</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>5</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CE_ACONTa_P25516</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>195.7398277820841</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>5</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CE_ACONTb_P25516</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>140.0358922751531</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>5</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CE_ACONTb_P25516</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>11.91322248613984</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>5</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>P27302</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>CE_TKT2_P27302</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>40.0974</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>5</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>P27302</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CE_TKT2_P27302</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>53.17969999999999</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>5</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>P27302</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CE_TKT1_P27302</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>5</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>P27302</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CE_TKT1_P27302</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>5</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>P33570</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CE_TKT1_P33570</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>126.8560977863716</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>5</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>P33570</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CE_TKT2_P33570</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>20.20817342021875</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>5</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>P33570</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CE_TKT2_P33570</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>3.976768775946323</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>5</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>P33570</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CE_TKT1_P33570</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>95.93011631521209</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>5</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>P39344</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>CE_IDONt2rpp_P39344</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>5</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>P39344</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CE_5DGLCNt2rpp_P39344</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>5</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>P39344</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>CE_5DGLCNt2rpp_P39344</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>5</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>P39344</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>CE_GLCNt2rpp_P39344</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>115.9664314426405</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>5</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>P39344</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>CE_GLCNt2rpp_P39344</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.8731407311056111</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>5</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>P39344</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CE_IDONt2rpp_P39344</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.8731407311056111</v>
       </c>
     </row>
   </sheetData>
@@ -2684,10 +6220,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1623.892132153967</v>
+        <v>1442.190232696943</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4510811478205465</v>
+        <v>0.400608397971373</v>
       </c>
     </row>
     <row r="3">
@@ -2695,10 +6231,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1308.17223114497</v>
+        <v>1048.563737913035</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3633811753180473</v>
+        <v>0.291267704975843</v>
       </c>
     </row>
     <row r="4">
@@ -2706,10 +6242,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1316.794678521925</v>
+        <v>1044.580941179069</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3657762995894235</v>
+        <v>0.2901613725497413</v>
       </c>
     </row>
     <row r="5">
@@ -2717,10 +6253,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1631.304740875959</v>
+        <v>1045.100370767061</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4531402057988776</v>
+        <v>0.2903056585464057</v>
       </c>
     </row>
     <row r="6">
@@ -2728,10 +6264,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1960.184663466061</v>
+        <v>5632.975378422998</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5444957398516838</v>
+        <v>1.564715382895277</v>
       </c>
     </row>
   </sheetData>
@@ -2765,7 +6301,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.004848047646733328</v>
+        <v>0.1761664429127696</v>
       </c>
     </row>
     <row r="3">
@@ -2773,7 +6309,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.04875039285394014</v>
+        <v>0.7297184448934423</v>
       </c>
     </row>
     <row r="4">
@@ -2781,7 +6317,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.6807513075048128</v>
+        <v>0.7491683990373255</v>
       </c>
     </row>
     <row r="5">
@@ -2789,7 +6325,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.4362913429598975</v>
+        <v>0.7283140178311508</v>
       </c>
     </row>
     <row r="6">
@@ -2797,7 +6333,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.5074860284493411</v>
+        <v>0.7277190391006383</v>
       </c>
     </row>
   </sheetData>
@@ -2811,7 +6347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2830,6 +6366,11 @@
           <t>intercept</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sector_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2838,10 +6379,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.004340256958025938</v>
+        <v>-0.00434025695802594</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04613664490966111</v>
+        <v>0.0461366449096611</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TranslationalProteinSector</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EX_glc__D_e</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.01116204915203404</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1429068958267162</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UnusedEnzymeSector</t>
+        </is>
       </c>
     </row>
   </sheetData>
